--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59482,6 +59482,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2571">
+      <c r="A2571" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2571" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2571" t="n">
+        <v>29.4650001525879</v>
+      </c>
+      <c r="D2571" t="n">
+        <v>29.4650001525879</v>
+      </c>
+      <c r="E2571" t="n">
+        <v>29.4650001525879</v>
+      </c>
+      <c r="F2571" t="n">
+        <v>29.4650001525879</v>
+      </c>
+      <c r="G2571" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2572" t="n">
+        <v>160</v>
+      </c>
+      <c r="C2572" t="n">
+        <v>29.5200004577637</v>
+      </c>
+      <c r="D2572" t="n">
+        <v>29.4500007629395</v>
+      </c>
+      <c r="E2572" t="n">
+        <v>29.4500007629395</v>
+      </c>
+      <c r="F2572" t="n">
+        <v>29.5200004577637</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59528,6 +59528,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2573">
+      <c r="A2573" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2573" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2573" t="n">
+        <v>29</v>
+      </c>
+      <c r="D2573" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2573" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2573" t="n">
+        <v>29</v>
+      </c>
+      <c r="G2573" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59551,6 +59551,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2574">
+      <c r="A2574" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2574" t="n">
+        <v>126</v>
+      </c>
+      <c r="C2574" t="n">
+        <v>27.8999996185303</v>
+      </c>
+      <c r="D2574" t="n">
+        <v>26.8050003051758</v>
+      </c>
+      <c r="E2574" t="n">
+        <v>27.8999996185303</v>
+      </c>
+      <c r="F2574" t="n">
+        <v>26.8050003051758</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59574,6 +59574,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59415,22 +59415,22 @@
     </row>
     <row r="2568">
       <c r="A2568" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2568" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C2568" t="n">
-        <v>28.4200000762939</v>
+        <v>28.0049991607666</v>
       </c>
       <c r="D2568" t="n">
-        <v>28.4200000762939</v>
+        <v>28.0049991607666</v>
       </c>
       <c r="E2568" t="n">
-        <v>28.4200000762939</v>
+        <v>28.0049991607666</v>
       </c>
       <c r="F2568" t="n">
-        <v>28.4200000762939</v>
+        <v>28.0049991607666</v>
       </c>
       <c r="G2568" t="s">
         <v>7</v>
@@ -59438,22 +59438,22 @@
     </row>
     <row r="2569">
       <c r="A2569" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2569" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C2569" t="n">
-        <v>29.4650001525879</v>
+        <v>28.4200000762939</v>
       </c>
       <c r="D2569" t="n">
-        <v>29.2600002288818</v>
+        <v>28.4200000762939</v>
       </c>
       <c r="E2569" t="n">
-        <v>29.2600002288818</v>
+        <v>28.4200000762939</v>
       </c>
       <c r="F2569" t="n">
-        <v>29.4650001525879</v>
+        <v>28.4200000762939</v>
       </c>
       <c r="G2569" t="s">
         <v>7</v>
@@ -59461,19 +59461,19 @@
     </row>
     <row r="2570">
       <c r="A2570" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2570" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C2570" t="n">
         <v>29.4650001525879</v>
       </c>
       <c r="D2570" t="n">
-        <v>29.4650001525879</v>
+        <v>29.2600002288818</v>
       </c>
       <c r="E2570" t="n">
-        <v>29.4650001525879</v>
+        <v>29.2600002288818</v>
       </c>
       <c r="F2570" t="n">
         <v>29.4650001525879</v>
@@ -59484,7 +59484,7 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2571" t="n">
         <v>0</v>
@@ -59507,22 +59507,22 @@
     </row>
     <row r="2572">
       <c r="A2572" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2572" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="C2572" t="n">
-        <v>29.5200004577637</v>
+        <v>29.4650001525879</v>
       </c>
       <c r="D2572" t="n">
-        <v>29.4500007629395</v>
+        <v>29.4650001525879</v>
       </c>
       <c r="E2572" t="n">
-        <v>29.4500007629395</v>
+        <v>29.4650001525879</v>
       </c>
       <c r="F2572" t="n">
-        <v>29.5200004577637</v>
+        <v>29.4650001525879</v>
       </c>
       <c r="G2572" t="s">
         <v>7</v>
@@ -59530,22 +59530,22 @@
     </row>
     <row r="2573">
       <c r="A2573" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2573" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="C2573" t="n">
-        <v>29</v>
+        <v>29.5200004577637</v>
       </c>
       <c r="D2573" t="n">
-        <v>29</v>
+        <v>29.4500007629395</v>
       </c>
       <c r="E2573" t="n">
-        <v>29</v>
+        <v>29.4500007629395</v>
       </c>
       <c r="F2573" t="n">
-        <v>29</v>
+        <v>29.5200004577637</v>
       </c>
       <c r="G2573" t="s">
         <v>7</v>
@@ -59553,22 +59553,22 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2574" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C2574" t="n">
-        <v>27.8999996185303</v>
+        <v>29</v>
       </c>
       <c r="D2574" t="n">
-        <v>26.8050003051758</v>
+        <v>29</v>
       </c>
       <c r="E2574" t="n">
-        <v>27.8999996185303</v>
+        <v>29</v>
       </c>
       <c r="F2574" t="n">
-        <v>26.8050003051758</v>
+        <v>29</v>
       </c>
       <c r="G2574" t="s">
         <v>7</v>
@@ -59576,22 +59576,22 @@
     </row>
     <row r="2575">
       <c r="A2575" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2575" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C2575" t="n">
-        <v>28.0049991607666</v>
+        <v>27.8999996185303</v>
       </c>
       <c r="D2575" t="n">
-        <v>28.0049991607666</v>
+        <v>26.8050003051758</v>
       </c>
       <c r="E2575" t="n">
-        <v>28.0049991607666</v>
+        <v>27.8999996185303</v>
       </c>
       <c r="F2575" t="n">
-        <v>28.0049991607666</v>
+        <v>26.8050003051758</v>
       </c>
       <c r="G2575" t="s">
         <v>7</v>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59597,6 +59597,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2576">
+      <c r="A2576" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2576" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2576" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2576" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2576" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2576" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59643,6 +59643,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2578">
+      <c r="A2578" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2578" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2578" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2578" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2578" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2578" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59666,6 +59666,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2579">
+      <c r="A2579" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2579" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2579" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2579" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2579" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2579" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2579" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59689,6 +59689,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2580">
+      <c r="A2580" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2580" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2580" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2580" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2580" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2580" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2580" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59712,6 +59712,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59735,6 +59735,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59758,6 +59758,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59781,6 +59781,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2584">
+      <c r="A2584" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2584" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2584" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2584" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2584" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2584" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59804,6 +59804,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59827,6 +59827,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2586">
+      <c r="A2586" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2586" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2586" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2586" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2586" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2586" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2586" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59850,6 +59850,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2587">
+      <c r="A2587" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2587" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2587" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2587" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2587" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2587" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2587" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59873,6 +59873,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2588">
+      <c r="A2588" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2588" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2588" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2588" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2588" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2588" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2588" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59896,6 +59896,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2589">
+      <c r="A2589" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2589" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2589" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2589" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2589" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2589" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2589" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59919,6 +59919,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2590">
+      <c r="A2590" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2590" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2590" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2590" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2590" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59942,6 +59942,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2591">
+      <c r="A2591" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2591" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2591" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2591" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2591" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2591" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2591" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -59988,6 +59988,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2593" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2593" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -60011,6 +60011,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2594">
+      <c r="A2594" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2594" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2594" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2594" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2594" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2594" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2594" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -60034,6 +60034,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -60057,6 +60057,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75691,6 +75691,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2598">
+      <c r="A2598" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2598" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2598" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2598" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2598" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2598" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2598" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2598" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2598" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75720,6 +75720,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2599">
+      <c r="A2599" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2599" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2599" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2599" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2599" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2599" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2599" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2599" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2599" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75749,6 +75749,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2600">
+      <c r="A2600" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2600" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2600" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2600" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2600" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2600" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2600" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2600" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75778,6 +75778,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2601">
+      <c r="A2601" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2601" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2601" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2601" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2601" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2601" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2601" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2601" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2601" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75807,6 +75807,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2602">
+      <c r="A2602" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2602" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2602" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2602" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2602" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2602" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2602" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2602" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2602" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75836,6 +75836,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2603">
+      <c r="A2603" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2603" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2603" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2603" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2603" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2603" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2603" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2603" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75865,6 +75865,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2604">
+      <c r="A2604" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2604" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2604" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2604" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2604" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2604" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2604" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2604" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2604" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75894,6 +75894,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2605">
+      <c r="A2605" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2605" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2605" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2605" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2605" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2605" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2605" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2605" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AIM.MI.xlsx
+++ b/data/AIM.MI.xlsx
@@ -75923,6 +75923,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2606">
+      <c r="A2606" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2606" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2606" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="D2606" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="E2606" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="G2606" t="n">
+        <v>28.0049991607666</v>
+      </c>
+      <c r="H2606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2606" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
